--- a/AAII_Financials/Quarterly/SBSW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBSW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>SBSW</t>
   </si>
@@ -656,24 +656,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -681,316 +681,342 @@
     <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2743600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2635900</v>
+      </c>
+      <c r="F8" s="3">
         <v>2262200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>2168400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1542200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1490400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1507400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1649500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1512000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1461000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1451900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1407600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1607800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1709500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1997200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>3938600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>2937400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>2617200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1267800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1661200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1587400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1755800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1279600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>945000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>840400</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1714700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1647400</v>
+      </c>
+      <c r="F9" s="3">
         <v>1797800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1723200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1077700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1041500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1513300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1655900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1316400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1272000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1498800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1453100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1192900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1268300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1605700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>2369400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>2220700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>2121800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1276900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1583900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1516400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1573800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1242100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>788400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>658500</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>464400</v>
+        <v>1028900</v>
       </c>
       <c r="E10" s="3">
-        <v>445100</v>
+        <v>988500</v>
       </c>
       <c r="F10" s="3">
         <v>464400</v>
       </c>
       <c r="G10" s="3">
+        <v>445100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>464400</v>
+      </c>
+      <c r="I10" s="3">
         <v>448800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>-5900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-6400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>195600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>189000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>-46900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>-45400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>414900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>441100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>391400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1569200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>716700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>495400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>-9100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>77400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>71000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>182100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>37500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>156700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>181900</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1017,8 +1043,10 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1088,11 +1116,17 @@
       <c r="Y12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z12" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1165,130 +1199,142 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E14" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F14" s="3">
         <v>121500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>116400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>13400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>12900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>6000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>6500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-4500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-4400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>228700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>221800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-3600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>-3800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>9400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>89500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>22000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>51000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>-15000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>201200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>23000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>154400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>222800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>-81400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>55500</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>129200</v>
+      </c>
+      <c r="E15" s="3">
+        <v>124100</v>
+      </c>
+      <c r="F15" s="3">
         <v>2900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>2800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>389100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>376100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>-68500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>-74900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>322000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>311200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>922900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>894700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>125600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>133500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>-94800</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
       <c r="S15" s="3">
         <v>0</v>
       </c>
@@ -1313,8 +1359,14 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1338,156 +1390,170 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1922000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1846500</v>
+      </c>
+      <c r="F17" s="3">
         <v>1955900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1874800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1544900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1493000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1538500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1683600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1704200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1646800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2546600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2468900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1375800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1462800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1580200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2470600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2258600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>2183400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1270700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1795300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1548400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1735800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1472600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>727500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>721900</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>821600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>789400</v>
+      </c>
+      <c r="F18" s="3">
         <v>306300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>293600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-2700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-2600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-31100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-34100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-192200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-185700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-1094700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-1061300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>232000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>246700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>416900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>1467900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>678900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>433800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-2900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-134100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>39000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>20000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-193000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>217600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>118500</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1514,378 +1580,410 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F20" s="3">
         <v>92200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>88400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>13900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>13400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-112100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-122600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-55800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-53900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>40400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>39200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-60400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-64200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>103300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-138400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>2700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-328300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-74600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>104800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>37000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-85200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-76400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-84500</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>960300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>922600</v>
+      </c>
+      <c r="F21" s="3">
         <v>217000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>208000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>372600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>360100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>12500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>13600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>185600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>179400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-212200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-205800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>418000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>444400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>218800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1367900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>865400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>177800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>80100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-2900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>281500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-18700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-103100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>217300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>145100</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>53600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>51500</v>
+      </c>
+      <c r="F22" s="3">
         <v>58600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>56100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>57500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>55600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>47900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>52400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>48200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>46600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>32600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>31600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>33900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>36000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>30100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>39900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>52500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>51900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>47100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>70100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>65200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>77100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>78000</v>
       </c>
-      <c r="Y22" s="3" t="s">
+      <c r="AA22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z22" s="3" t="s">
+      <c r="AB22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>796200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>765000</v>
+      </c>
+      <c r="F23" s="3">
         <v>60700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>58200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-68200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-65900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>42700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>46700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-159600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-154200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-1378700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1336600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>281100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>298900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>292200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1289600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>629000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>53600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-124600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-99400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>10800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-142300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-347400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>208700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>222700</v>
+      </c>
+      <c r="E24" s="3">
+        <v>214000</v>
+      </c>
+      <c r="F24" s="3">
         <v>85900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>82300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>41800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>40400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>8500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>9300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>32200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>31100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-142700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-138300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>74400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>79100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>96900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>152800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>109500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>21600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-115400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>62100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>5600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-166600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-27600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>39800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>28900</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1958,156 +2056,174 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>573500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>551000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-25200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-24100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-110000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-106300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>34200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>37400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-191800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-185300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-1236000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1198300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>206700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>219800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>195300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>1136900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>519500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>32000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-9200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-161400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>5200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>24300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-319800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>168900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>541100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>519900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-47700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-45700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-101100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-97700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-200900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-194100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1235400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1197700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>197000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>209500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>187600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>1084400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>501100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>16800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-13700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-160000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>5100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>24100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-319800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>179500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2180,8 +2296,14 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2254,8 +2376,14 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2328,8 +2456,14 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2402,156 +2536,174 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-92200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-88400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-13900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-13400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>112100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>122600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>55800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>53900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-40400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-39200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>60400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>64200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-103300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>138400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-2700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>328300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>74600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-104800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-37000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>85200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>76400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>8900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>84500</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>541100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>519900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-47700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-45700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-101100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-97700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-200900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-194100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1235400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1197700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>197000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>209500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>187600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>1084400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>501100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>16800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-13700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-160000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>5100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>24100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-319800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>179500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2624,161 +2776,179 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>541100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>519900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-47700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-45700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-101100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-97700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-200900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-194100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1235400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1197700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>197000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>209500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>187600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>1084400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>501100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>16800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-13700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-160000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>5100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>24100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-319800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>179500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2805,8 +2975,10 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2833,82 +3005,90 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1368100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1314400</v>
+      </c>
+      <c r="F41" s="3">
         <v>1037500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>994500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1183300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1143600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>850000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>930100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>852400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>823600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1397400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1354700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1176400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1250800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1533800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1101400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>642800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>297800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>321300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>158300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>139400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>135700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>434300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>55300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>49800</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2981,182 +3161,200 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>572600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>550100</v>
+      </c>
+      <c r="F43" s="3">
         <v>688800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>660300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>603800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>583500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>315000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>344700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>553400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>534800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>474500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>460100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>466300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>495800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>463000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>383700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>258000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>267100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>295100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>456600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>434600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>422000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>389000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>346200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1941200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1865000</v>
+      </c>
+      <c r="F44" s="3">
         <v>1901300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1822500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1595700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1542100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1353100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1480700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1416900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1369200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1441300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1397300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1365000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1451300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1551900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>1357900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>898200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>821500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>765500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>328900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>281200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>232000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>197200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>38700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>16600</v>
+      </c>
+      <c r="F45" s="3">
         <v>1800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>17200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>16600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>3700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>4100</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>8</v>
@@ -3182,325 +3380,355 @@
       <c r="S45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T45" s="3">
-        <v>6500</v>
+      <c r="T45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V45" s="3">
-        <v>84300</v>
+        <v>6500</v>
       </c>
       <c r="W45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="3" t="s">
+        <v>84300</v>
+      </c>
+      <c r="Y45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3899300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3746200</v>
+      </c>
+      <c r="F46" s="3">
         <v>3669300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3517100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3400100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3285900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>2563800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2805500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2822700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2727600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>3379800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>3276700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3007700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3197900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>3574100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2843000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1799000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1386400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1388400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>943800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>939500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>789700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1020500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>440200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>203200</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>740100</v>
+      </c>
+      <c r="E47" s="3">
+        <v>711000</v>
+      </c>
+      <c r="F47" s="3">
         <v>654200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>627000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>541500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>523400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>573600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>627600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>585400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>565700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>564600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>547400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>670400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>712800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>694700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>350600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>326200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>250200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>242700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>251400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>197500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>166300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>174400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>143600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>131700</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4169600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>4006000</v>
+      </c>
+      <c r="F48" s="3">
         <v>3916800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3754400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3531000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3412400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3551700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3886500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3388900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3274600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3384000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>3280800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>4960500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>5274200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>4540200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>3313900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>3535500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>3065000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>3057100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>3388600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>3532300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>3384000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>3620500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>1556800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>1326500</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>113400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>108900</v>
+      </c>
+      <c r="F49" s="3">
         <v>119200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>114200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>112300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>108500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>114100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>124800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>108100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>104400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>27400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>26600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>485800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>516600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>489500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>389900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>446400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>363200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>371400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>427900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>465500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>420700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>453400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>53500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>55000</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3573,8 +3801,14 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3647,82 +3881,94 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>749600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>720200</v>
+      </c>
+      <c r="F52" s="3">
         <v>557800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>534600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>438800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>424000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>380400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>416200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>377000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>364300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>352600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>341900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>337100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>358400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>359000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>400400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>311400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>290900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>273300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>262800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>248400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>243300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>227000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>190200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>159700</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3795,82 +4041,94 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9723000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>9341400</v>
+      </c>
+      <c r="F54" s="3">
         <v>9043600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>8668600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>8149000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>7875300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>7313300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>8002700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>7390400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>7141300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>7814600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>7576300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>9578900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>10184600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>9801100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>7297900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>6418700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>5355800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>5332800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>5274600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>5383200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>5004000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>5495800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>2384400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1876100</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3897,8 +4155,10 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3925,452 +4185,490 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1113600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1069900</v>
+      </c>
+      <c r="F57" s="3">
         <v>205700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>197200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>876100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>846700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>210900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>230800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>843500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>815100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>233900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>226700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>816400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>868000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>243900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>718700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>631000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>607600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>598600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>488000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>453700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>440100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>476300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>296100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>221800</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>24300</v>
+      </c>
+      <c r="F58" s="3">
         <v>698700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>669700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>25900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>25000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>38500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>42100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>268000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>259000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>857200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>831100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>17800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>18900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>13700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>53800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>73400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>7900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>298800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>384300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>22200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>109000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>504100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>43000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>216000</v>
       </c>
     </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>247200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>237500</v>
+      </c>
+      <c r="F59" s="3">
         <v>357800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>343000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>247400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>239100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>284100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>310900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>232600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>224800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>252700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>245000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>78200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>83100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>310600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>179100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>211600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>143700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>199200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>36500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>31900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>5900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>9300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>18500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1433700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1377400</v>
+      </c>
+      <c r="F60" s="3">
         <v>2063000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1977500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1176900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1137400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1109600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1214200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1353000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1307400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1990400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1929700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>956800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1017300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1189300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>951600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>916000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>759200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1096600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>908800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>507900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>555000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>989700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>357600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>466900</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2252000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2163600</v>
+      </c>
+      <c r="F61" s="3">
         <v>1953000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1872000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2387700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2307500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2189300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2395700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1801500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1740800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1384800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1342600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1360000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1446000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1341900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>964300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1352400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>1270200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1181600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1137600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>1882700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>1578200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>1507200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>469900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>185700</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1108000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1064600</v>
+      </c>
+      <c r="F62" s="3">
         <v>1114200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1068000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>912100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>881500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>835200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>913900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1072700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1036500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1043900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1012000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1055500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1122200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>990200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1533500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1693100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1676400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1424800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1692500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1298800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1292200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>1396700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>615700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>403300</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4443,8 +4741,14 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4517,8 +4821,14 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4591,82 +4901,94 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6114300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5874300</v>
+      </c>
+      <c r="F66" s="3">
         <v>6376100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>6111700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>5651600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>5461800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4755800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>5204200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4840900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4677700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>4993200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4841000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>4261100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>4530500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>4448300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>3571200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>4035800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>3783500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>3770300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>3797100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>3690800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>3426700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>3894700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1444200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1047600</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4693,8 +5015,10 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4767,8 +5091,14 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4841,8 +5171,14 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4915,8 +5251,14 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4989,82 +5331,94 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-307700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-295600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1152500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-1104700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-980400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-947400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-731800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-800700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-766500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-740600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-463100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-448900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>2029500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2157900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>1987000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>2085900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>212000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-582400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-628000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-675700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-609100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-703100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-709000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-301900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-413700</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5137,8 +5491,14 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5211,8 +5571,14 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5285,82 +5651,94 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3274600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3146100</v>
+      </c>
+      <c r="F76" s="3">
         <v>2387200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>2288300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2273600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2197300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2329200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>2548800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2377600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2297500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2664100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>2582800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>5149300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>5474900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>5182000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>3726700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>2382900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1572200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1562500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1477500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1692400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1577300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1601100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>940200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>828400</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5433,161 +5811,179 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>541100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>519900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-47700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-45700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-101100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-97700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-200900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-194100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1235400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1197700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>197000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>209500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>187600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>1084400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>501100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>16800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-13700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-160000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>5100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>24100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-319800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>179500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5614,56 +6010,58 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>118800</v>
+      </c>
+      <c r="E83" s="3">
+        <v>114800</v>
+      </c>
+      <c r="F83" s="3">
         <v>120500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>131800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>113200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>109400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>144200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>139800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>125600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>133500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>113500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>107100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>98500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>110200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>140800</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
@@ -5688,8 +6086,14 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5762,8 +6166,14 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5836,8 +6246,14 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5910,8 +6326,14 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5984,8 +6406,14 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6058,82 +6486,94 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>717800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>689600</v>
+      </c>
+      <c r="F89" s="3">
         <v>253800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>243200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>374700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>362100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>172200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>188400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>103600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>97800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>107500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>104200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>225200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>239400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>447900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>694500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>768200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>431200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>71500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>612600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>154900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>108400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>72800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>110500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>141300</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6160,82 +6600,90 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-253300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-243300</v>
+      </c>
+      <c r="F91" s="3">
         <v>-325200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-311700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-268600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-259600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-276000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-302000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-305300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-295000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-315900</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-306300</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-288100</v>
       </c>
       <c r="O91" s="3">
         <v>-306300</v>
       </c>
       <c r="P91" s="3">
+        <v>-288100</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>-306300</v>
+      </c>
+      <c r="R91" s="3">
         <v>-286900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-5481100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-4134500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-5122700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-139200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-249400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-203500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-237800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-165400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-136600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-100700</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6308,8 +6756,14 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6382,82 +6836,94 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-242800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-233200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-378600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-362900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-257800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-249200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-273400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-299100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-383900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-370900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-318700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-309000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-275500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-292900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-289700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-276100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-259700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-269800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>12200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-292800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-201100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-243000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-1627900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-223500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-316200</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6484,56 +6950,58 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>119700</v>
+      </c>
+      <c r="E96" s="3">
+        <v>115000</v>
+      </c>
+      <c r="F96" s="3">
         <v>5200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>5000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>3600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>3500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>2300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>2500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>2400</v>
       </c>
-      <c r="K96" s="3" t="s">
+      <c r="M96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>48600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>47100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>93900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>99900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>119800</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -6558,8 +7026,14 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6632,8 +7106,14 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6706,8 +7186,14 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6780,226 +7266,250 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-312100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-299900</v>
+      </c>
+      <c r="F100" s="3">
         <v>34100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>32700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>37300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>36000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>112100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>122700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>9000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>11000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>306700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>297300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-94600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-100500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-220500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>44800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-163800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-188000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>111900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-292100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>39900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-145300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>1931800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>118600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>192600</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="F101" s="3">
         <v>2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>2200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-2700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-2600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-2500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-2400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>40900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>43500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>27900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>26300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>5000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>5600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>24300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-17000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-1900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>6400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-9700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>8800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-13500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>160300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>154000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-115800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-111000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>139800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>135100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>12900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>14200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-273900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-264700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>93000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>90100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-104000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-110600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-34500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>446200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>342800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-20200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>185900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>27900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>2500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-293400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>369900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>5600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>8800</v>
       </c>
     </row>
